--- a/从零开始学Slots/从零开始学Slots-35-数值篇-MegaSymbols(2).xlsx
+++ b/从零开始学Slots/从零开始学Slots-35-数值篇-MegaSymbols(2).xlsx
@@ -7902,6 +7902,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:N161" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -8513,5 +8516,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:P68" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-35-数值篇-MegaSymbols(2).xlsx
+++ b/从零开始学Slots/从零开始学Slots-35-数值篇-MegaSymbols(2).xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="174">
   <si>
     <r>
       <rPr>
@@ -6840,7 +6840,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -6963,6 +6963,10 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -8439,8 +8443,8 @@
       <c r="H43" s="14"/>
     </row>
     <row r="44" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="17" t="s">
-        <v>167</v>
+      <c r="A44" s="31">
+        <v>4</v>
       </c>
       <c r="B44" s="25" t="str">
         <f aca="false">IF(ABS(C22-1)&lt;0.0001,"✓","✗")</f>

--- a/从零开始学Slots/从零开始学Slots-35-数值篇-MegaSymbols(2).xlsx
+++ b/从零开始学Slots/从零开始学Slots-35-数值篇-MegaSymbols(2).xlsx
@@ -6653,10 +6653,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00%"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -6840,7 +6841,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -6966,6 +6967,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" applyNumberFormat="1" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" applyNumberFormat="1" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -8165,7 +8174,7 @@
       <c r="A22" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="C22" s="20" t="n">
+      <c r="C22" s="33" t="n">
         <f aca="false">SUM(C18:C21)</f>
         <v>1</v>
       </c>
@@ -8210,7 +8219,7 @@
       <c r="B26" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="C26" s="20" t="n">
+      <c r="C26" s="33" t="n">
         <f aca="false">C18</f>
         <v>0.3</v>
       </c>
@@ -8227,7 +8236,7 @@
       <c r="B27" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="C27" s="20" t="n">
+      <c r="C27" s="33" t="n">
         <f aca="false">C19</f>
         <v>0.3</v>
       </c>
@@ -8244,7 +8253,7 @@
       <c r="B28" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="C28" s="20" t="n">
+      <c r="C28" s="33" t="n">
         <f aca="false">C20</f>
         <v>0.25</v>
       </c>
@@ -8261,7 +8270,7 @@
       <c r="B29" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="C29" s="20" t="n">
+      <c r="C29" s="33" t="n">
         <f aca="false">C21</f>
         <v>0.15</v>
       </c>
@@ -8274,7 +8283,7 @@
       <c r="A30" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="C30" s="20" t="n">
+      <c r="C30" s="33" t="n">
         <f aca="false">SUM(C26:C29)</f>
         <v>1</v>
       </c>
@@ -8328,7 +8337,7 @@
       <c r="A35" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="B35" s="20" t="n">
+      <c r="B35" s="33" t="n">
         <f aca="false">C26</f>
         <v>0.3</v>
       </c>
@@ -8344,7 +8353,7 @@
       <c r="A36" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="B36" s="20" t="n">
+      <c r="B36" s="33" t="n">
         <f aca="false">C27</f>
         <v>0.3</v>
       </c>
@@ -8360,7 +8369,7 @@
       <c r="A37" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="B37" s="20" t="n">
+      <c r="B37" s="33" t="n">
         <f aca="false">C28</f>
         <v>0.25</v>
       </c>
@@ -8376,7 +8385,7 @@
       <c r="A38" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="B38" s="20" t="n">
+      <c r="B38" s="33" t="n">
         <f aca="false">C29</f>
         <v>0.15</v>
       </c>
